--- a/artfynd/A 23010-2026 artfynd.xlsx
+++ b/artfynd/A 23010-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120474496</v>
+        <v>120474494</v>
       </c>
       <c r="B2" t="n">
-        <v>97087</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749703</v>
+        <v>749770</v>
       </c>
       <c r="R2" t="n">
-        <v>7079088</v>
+        <v>7078993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0,2 kvm</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +775,7 @@
         <v>120474497</v>
       </c>
       <c r="B3" t="n">
-        <v>105223</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120474494</v>
+        <v>120474495</v>
       </c>
       <c r="B4" t="n">
-        <v>78631</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749770</v>
+        <v>749663</v>
       </c>
       <c r="R4" t="n">
-        <v>7078993</v>
+        <v>7079025</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1kvm</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120474495</v>
+        <v>120474496</v>
       </c>
       <c r="B5" t="n">
-        <v>97087</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749663</v>
+        <v>749703</v>
       </c>
       <c r="R5" t="n">
-        <v>7079025</v>
+        <v>7079088</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1kvm</t>
+          <t>0,2 kvm</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 23010-2026 artfynd.xlsx
+++ b/artfynd/A 23010-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120474494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120474497</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120474495</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,8 +1095,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120474496</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>